--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484586_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484586_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4117</v>
+        <v>2.2666</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5982</v>
+        <v>3.3788</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1865</v>
+        <v>-1.1122</v>
       </c>
       <c r="G2" t="n">
         <v>0.2475</v>
@@ -610,13 +610,13 @@
         <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0201</v>
+        <v>0.875</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7496</v>
+        <v>0.5302</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2705</v>
+        <v>0.3448</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2027</v>
+        <v>2.1375</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5036</v>
+        <v>5.1907</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3009</v>
+        <v>-3.0532</v>
       </c>
       <c r="G3" t="n">
         <v>0.6612</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1915</v>
+        <v>-0.2568</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.0837</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4208</v>
+        <v>-0.1731</v>
       </c>
       <c r="V3" t="n">
         <v>0.6335</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8746</v>
+        <v>1.0199</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3378</v>
+        <v>1.6813</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4632</v>
+        <v>-0.6614</v>
       </c>
       <c r="G4" t="n">
         <v>2.2731</v>
@@ -766,13 +766,13 @@
         <v>2.0158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4247</v>
+        <v>-0.2794</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3869</v>
+        <v>-0.0433</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0379</v>
+        <v>-0.2361</v>
       </c>
       <c r="V4" t="n">
         <v>-1.89</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5228</v>
+        <v>-1.4981</v>
       </c>
       <c r="E5" t="n">
         <v>-0.1001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4227</v>
+        <v>-1.3979</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5288</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2768</v>
+        <v>-0.2521</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1117</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.267</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7725</v>
+        <v>-1.5311</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.1064</v>
+        <v>-2.6667</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3338</v>
+        <v>1.1357</v>
       </c>
       <c r="G6" t="n">
         <v>-1.7589</v>
@@ -922,13 +922,13 @@
         <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0.125</v>
+        <v>0.3665</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4404</v>
+        <v>-0.0007</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5654</v>
+        <v>0.3673</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6207</v>
+        <v>-1.8838</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5711</v>
+        <v>-2.1314</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0496</v>
+        <v>0.2476</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1326</v>
@@ -1000,13 +1000,13 @@
         <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1766</v>
+        <v>-0.4397</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6606</v>
+        <v>-0.221</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.516</v>
+        <v>-0.2187</v>
       </c>
       <c r="V7" t="n">
         <v>-0.945</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.7881</v>
+        <v>-3.4289</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6178</v>
+        <v>1.2004</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1703</v>
+        <v>-4.6293</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3333</v>
+        <v>0.0433</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.6633</v>
+        <v>0.2998</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.67</v>
+        <v>-0.2564</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3607</v>
+        <v>3.1974</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.7871</v>
+        <v>1.1455</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5736</v>
+        <v>2.0519</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9726</v>
+        <v>-3.154</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8762</v>
+        <v>-0.8457</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0964</v>
+        <v>-2.3083</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.2986</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.5814</v>
+        <v>-2.9321</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8646</v>
+        <v>-0.6005</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6908</v>
+        <v>-0.3318</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1737</v>
+        <v>-0.2687</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0208</v>
+        <v>-1.5889</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6543</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.377</v>
+        <v>-3.7607</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3761</v>
+        <v>-1.7286</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.7531</v>
+        <v>-2.0321</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0433</v>
+        <v>-5.98</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2998</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2564</v>
+        <v>-5.9076</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1974</v>
+        <v>-2.9801</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1455</v>
+        <v>0.0742</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0519</v>
+        <v>-3.0544</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.154</v>
+        <v>-2.9999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8457</v>
+        <v>-0.1466</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3083</v>
+        <v>-2.8532</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9321</v>
+        <v>-0.1833</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5486</v>
+        <v>-0.1472</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1561</v>
+        <v>0.1678</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3925</v>
+        <v>-0.3151</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5889</v>
+        <v>1.267</v>
       </c>
       <c r="W9" t="n">
         <v>1.267</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.656</v>
+        <v>-4.2252</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0974</v>
+        <v>-3.3692</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5587</v>
+        <v>-0.8559</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9633</v>
@@ -1234,13 +1234,13 @@
         <v>2.7489</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5278</v>
+        <v>-0.0969</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0.0291</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1713</v>
+        <v>-0.126</v>
       </c>
       <c r="V10" t="n">
         <v>0.9346</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8619</v>
+        <v>-4.3202</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4955</v>
+        <v>-4.152</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3665</v>
+        <v>-0.1683</v>
       </c>
       <c r="G11" t="n">
         <v>-4.004</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4365</v>
+        <v>0.1052</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3122</v>
+        <v>0.0313</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1243</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0.3115</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0087</v>
+        <v>-5.2605</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7041</v>
+        <v>-4.9911</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3046</v>
+        <v>-0.2694</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.98</v>
+        <v>-3.3333</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-2.6633</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.9076</v>
+        <v>-0.67</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9801</v>
+        <v>-2.3607</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0742</v>
+        <v>-1.7871</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.0544</v>
+        <v>-0.5736</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9999</v>
+        <v>-0.9726</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1466</v>
+        <v>-0.8762</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.8532</v>
+        <v>-0.0964</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0995</v>
+        <v>-3.2986</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1833</v>
+        <v>-4.5814</v>
       </c>
       <c r="R12" t="n">
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3952</v>
+        <v>1.3922</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8077</v>
+        <v>1.3175</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5876</v>
+        <v>0.0746</v>
       </c>
       <c r="V12" t="n">
-        <v>1.267</v>
+        <v>-0.0208</v>
       </c>
       <c r="W12" t="n">
-        <v>1.267</v>
+        <v>0.6335</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8785</v>
+        <v>-8.411899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8357</v>
+        <v>-5.9232</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0428</v>
+        <v>-2.4887</v>
       </c>
       <c r="G13" t="n">
         <v>-9.4573</v>
@@ -1468,13 +1468,13 @@
         <v>2.5656</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2465</v>
+        <v>1.713</v>
       </c>
       <c r="T13" t="n">
-        <v>3.678</v>
+        <v>1.5905</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5684</v>
+        <v>0.1225</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3011</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.9972</v>
+        <v>-28.8964</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.7124</v>
+        <v>-13.6111</v>
       </c>
       <c r="F14" t="n">
         <v>-15.2851</v>
@@ -1519,7 +1519,7 @@
         <v>-9.616900000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.972099999999999</v>
+        <v>-2.9721</v>
       </c>
       <c r="K14" t="n">
         <v>-6.180199999999999</v>
@@ -1537,7 +1537,7 @@
         <v>-12.8251</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.832400000000001</v>
+        <v>-1.8324</v>
       </c>
       <c r="Q14" t="n">
         <v>-20.1583</v>
@@ -1546,13 +1546,13 @@
         <v>18.3257</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2785</v>
+        <v>2.3793</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7195</v>
+        <v>2.8207</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4415</v>
+        <v>-0.4415000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-3.51</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.624700000000001</v>
+        <v>9.648099999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.083</v>
+        <v>6.6022</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5417</v>
+        <v>3.0458</v>
       </c>
       <c r="G15" t="n">
         <v>7.0629</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0.0234</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.434</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.4107</v>
       </c>
       <c r="V15" t="n">
         <v>1.4622</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8692</v>
+        <v>6.5189</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5711</v>
+        <v>3.3403</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2981</v>
+        <v>3.1786</v>
       </c>
       <c r="G16" t="n">
         <v>7.0805</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4744</v>
+        <v>0.1753</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5513</v>
+        <v>0.218</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0769</v>
+        <v>-0.0426</v>
       </c>
       <c r="V16" t="n">
         <v>1.4622</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9973</v>
+        <v>4.3033</v>
       </c>
       <c r="E17" t="n">
         <v>1.6756</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3217</v>
+        <v>2.6277</v>
       </c>
       <c r="G17" t="n">
         <v>0.4417</v>
@@ -1780,13 +1780,13 @@
         <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1502</v>
+        <v>0.1557</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1306</v>
+        <v>0.1753</v>
       </c>
       <c r="V17" t="n">
         <v>1.1403</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.9054</v>
+        <v>4.1026</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4149</v>
+        <v>2.9019</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4905</v>
+        <v>1.2007</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1427</v>
+        <v>4.2381</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7035</v>
+        <v>3.7959</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4392</v>
+        <v>0.4422</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4715</v>
+        <v>4.3945</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2627</v>
+        <v>2.926</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2087</v>
+        <v>1.4684</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6712</v>
+        <v>-0.1564</v>
       </c>
       <c r="N18" t="n">
-        <v>1.4407</v>
+        <v>0.8698</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7695</v>
+        <v>-1.0262</v>
       </c>
       <c r="P18" t="n">
-        <v>2.7489</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7489</v>
+        <v>2.9321</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3972</v>
+        <v>0.1195</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0565</v>
+        <v>-0.0211</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3407</v>
+        <v>0.1406</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5889</v>
+        <v>-0.4382</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2774</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.5889</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.8375</v>
+        <v>3.9913</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5173</v>
+        <v>2.3188</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3202</v>
+        <v>1.6726</v>
       </c>
       <c r="G19" t="n">
-        <v>4.2381</v>
+        <v>3.1427</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7959</v>
+        <v>1.7035</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4422</v>
+        <v>1.4392</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3945</v>
+        <v>2.4715</v>
       </c>
       <c r="K19" t="n">
-        <v>2.926</v>
+        <v>0.2627</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4684</v>
+        <v>2.2087</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1564</v>
+        <v>0.6712</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8698</v>
+        <v>1.4407</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0262</v>
+        <v>-0.7695</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>2.7489</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9321</v>
+        <v>2.7489</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1456</v>
+        <v>-0.3113</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4057</v>
+        <v>-0.1527</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2601</v>
+        <v>-0.1586</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4382</v>
+        <v>-1.5889</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2774</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7156</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.645</v>
+        <v>3.0107</v>
       </c>
       <c r="E20" t="n">
-        <v>2.367</v>
+        <v>2.5593</v>
       </c>
       <c r="F20" t="n">
-        <v>0.278</v>
+        <v>0.4514</v>
       </c>
       <c r="G20" t="n">
         <v>1.2686</v>
@@ -2014,13 +2014,13 @@
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1408</v>
+        <v>0.2249</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0166</v>
+        <v>0.2089</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1574</v>
+        <v>0.016</v>
       </c>
       <c r="V20" t="n">
         <v>1.1507</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6157</v>
+        <v>1.69</v>
       </c>
       <c r="E21" t="n">
         <v>1.5824</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0332</v>
+        <v>0.1076</v>
       </c>
       <c r="G21" t="n">
         <v>0.8754</v>
@@ -2092,13 +2092,13 @@
         <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6654</v>
+        <v>-0.5911</v>
       </c>
       <c r="T21" t="n">
         <v>-0.4404</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.225</v>
+        <v>-0.1506</v>
       </c>
       <c r="V21" t="n">
         <v>1.5889</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.678</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7163</v>
+        <v>0.9086</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0382</v>
+        <v>0.0113</v>
       </c>
       <c r="G22" t="n">
         <v>0.6820000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0.733</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4255</v>
+        <v>-0.1836</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3854</v>
+        <v>-0.1931</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0401</v>
+        <v>0.0094</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3115</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. SORIANO ZORIO</t>
+          <t>A. DEMBELE CUESTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3376</v>
+        <v>-0.173</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1712</v>
+        <v>0.2949</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5088</v>
+        <v>-0.4679</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0396</v>
+        <v>1.0604</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6722</v>
+        <v>-0.3597</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7118</v>
+        <v>1.4201</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1055</v>
+        <v>1.3353</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.0873</v>
+        <v>0.0433</v>
       </c>
       <c r="L24" t="n">
-        <v>2.1928</v>
+        <v>1.2919</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0659</v>
+        <v>-0.2748</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4151</v>
+        <v>-0.403</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.481</v>
+        <v>0.1282</v>
       </c>
       <c r="P24" t="n">
+        <v>-0.5498</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9163</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.3665</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-1.8326</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.1991</v>
-      </c>
       <c r="S24" t="n">
-        <v>1.5204</v>
+        <v>-0.0502</v>
       </c>
       <c r="T24" t="n">
-        <v>1.5558</v>
+        <v>-0.1241</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0355</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5889</v>
+        <v>-0.6335</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.5889</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. DEMBELE CUESTA</t>
+          <t>J. SORIANO ZORIO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2691</v>
+        <v>-0.4957</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1988</v>
+        <v>-1.1327</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4679</v>
+        <v>0.637</v>
       </c>
       <c r="G25" t="n">
-        <v>1.0604</v>
+        <v>0.0396</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3597</v>
+        <v>-1.6722</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4201</v>
+        <v>1.7118</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3353</v>
+        <v>0.1055</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0433</v>
+        <v>-2.0873</v>
       </c>
       <c r="L25" t="n">
-        <v>1.2919</v>
+        <v>2.1928</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2748</v>
+        <v>-0.0659</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.403</v>
+        <v>0.4151</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1282</v>
+        <v>-0.481</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3665</v>
+        <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1463</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2202</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0927</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6335</v>
+        <v>-1.5889</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6335</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4092</v>
+        <v>-1.1377</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6246</v>
+        <v>-3.1053</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2153</v>
+        <v>1.9676</v>
       </c>
       <c r="G26" t="n">
         <v>-0.1377</v>
@@ -2482,13 +2482,13 @@
         <v>1.2828</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8439</v>
+        <v>0.1154</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6026</v>
+        <v>0.1218</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2413</v>
+        <v>-0.0064</v>
       </c>
       <c r="V26" t="n">
         <v>1.267</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.4598</v>
+        <v>-1.7241</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.6706</v>
+        <v>-3.286</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2108</v>
+        <v>1.5619</v>
       </c>
       <c r="G27" t="n">
         <v>-0.4463</v>
@@ -2560,13 +2560,13 @@
         <v>0.9163</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0972</v>
+        <v>-0.3614</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5694</v>
+        <v>-0.1847</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5278</v>
+        <v>-0.1767</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>29.9974</v>
+        <v>31.2794</v>
       </c>
       <c r="E28" t="n">
         <v>15.2851</v>
       </c>
       <c r="F28" t="n">
-        <v>14.7122</v>
+        <v>15.9943</v>
       </c>
       <c r="G28" t="n">
         <v>25.933</v>
@@ -2608,7 +2608,7 @@
         <v>16.316</v>
       </c>
       <c r="I28" t="n">
-        <v>9.616899999999999</v>
+        <v>9.616900000000001</v>
       </c>
       <c r="J28" t="n">
         <v>22.9607</v>
@@ -2623,13 +2623,13 @@
         <v>2.9721</v>
       </c>
       <c r="N28" t="n">
-        <v>6.180100000000001</v>
+        <v>6.180099999999999</v>
       </c>
       <c r="O28" t="n">
         <v>-3.2081</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8325</v>
+        <v>1.832499999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-18.3258</v>
@@ -2638,13 +2638,13 @@
         <v>20.1582</v>
       </c>
       <c r="S28" t="n">
-        <v>-1.2783</v>
+        <v>0.003600000000000048</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4412999999999999</v>
+        <v>0.4413000000000002</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.7197</v>
+        <v>-0.4377000000000001</v>
       </c>
       <c r="V28" t="n">
         <v>3.5103</v>
